--- a/EG0A.xlsx
+++ b/EG0A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="90">
   <si>
     <t/>
   </si>
   <si>
-    <t>20113971</t>
-  </si>
-  <si>
-    <t>KURMA MEDJOOL  PCK</t>
+    <t>20070380</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN PCS</t>
   </si>
   <si>
     <t>EG0A</t>
@@ -28,21 +28,21 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-2H)</t>
+  </si>
+  <si>
+    <t>20046368</t>
+  </si>
+  <si>
+    <t>KURMA DATE CROWN 250</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20140218</t>
-  </si>
-  <si>
-    <t>KURMA TUNIS BRARI500</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-2H)</t>
-  </si>
-  <si>
     <t>20016388</t>
   </si>
   <si>
@@ -52,15 +52,18 @@
     <t>3</t>
   </si>
   <si>
-    <t>20140192</t>
-  </si>
-  <si>
-    <t>KURMA SAYER BRARI250</t>
+    <t>20015737</t>
+  </si>
+  <si>
+    <t>IDM NATA DE COCO 900</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20139288</t>
   </si>
   <si>
@@ -70,201 +73,117 @@
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10008882</t>
-  </si>
-  <si>
-    <t>K/API KOPI SPCL 150G</t>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
+  </si>
+  <si>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20140456</t>
+  </si>
+  <si>
+    <t>WONG COCO PEDAS 220G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20140229</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLUE3X120</t>
+  </si>
+  <si>
+    <t>20125696</t>
+  </si>
+  <si>
+    <t>WG.C PUDING MANGO 3S</t>
+  </si>
+  <si>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20137260</t>
+  </si>
+  <si>
+    <t>B/D FW ACNE CARE 100</t>
+  </si>
+  <si>
+    <t>20042866</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT150</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138098</t>
+  </si>
+  <si>
+    <t>SCORA GENTLE CLEAN75</t>
+  </si>
+  <si>
+    <t>20137173</t>
+  </si>
+  <si>
+    <t>SCRLETT EDP VEL.R 30</t>
+  </si>
+  <si>
+    <t>20137253</t>
+  </si>
+  <si>
+    <t>BRAVEN EDP COOL 100M</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20053183</t>
+  </si>
+  <si>
+    <t>GTSBY STYL POMADE 75</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>RT,(E-4B)</t>
   </si>
   <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20140456</t>
-  </si>
-  <si>
-    <t>WONG COCO PEDAS 220G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20140229</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLUE3X120</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20125696</t>
-  </si>
-  <si>
-    <t>WG.C PUDING MANGO 3S</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 400</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20093101</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS380</t>
-  </si>
-  <si>
-    <t>20049941</t>
-  </si>
-  <si>
-    <t>LUX BW MCG ORCHD 400</t>
-  </si>
-  <si>
-    <t>20038766</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 160</t>
-  </si>
-  <si>
-    <t>PT,(E-5B)</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>10012742</t>
-  </si>
-  <si>
-    <t>LISTERINE COOLMIN250</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20113402</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH E&amp;B 100</t>
-  </si>
-  <si>
-    <t>20137260</t>
-  </si>
-  <si>
-    <t>B/D FW ACNE CARE 100</t>
-  </si>
-  <si>
-    <t>20042866</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT150</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>20138098</t>
-  </si>
-  <si>
-    <t>SCORA GENTLE CLEAN75</t>
-  </si>
-  <si>
-    <t>20137173</t>
-  </si>
-  <si>
-    <t>SCRLETT EDP VEL.R 30</t>
-  </si>
-  <si>
-    <t>20137253</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP COOL 100M</t>
-  </si>
-  <si>
-    <t>20053183</t>
-  </si>
-  <si>
-    <t>GTSBY STYL POMADE 75</t>
-  </si>
-  <si>
     <t>20141306</t>
   </si>
   <si>
@@ -272,6 +191,93 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20071105</t>
+  </si>
+  <si>
+    <t>MITU GP PURPLE 2X50S</t>
+  </si>
+  <si>
+    <t>20132821</t>
+  </si>
+  <si>
+    <t>YNKN WIPE HND&amp;MTH2'S</t>
+  </si>
+  <si>
+    <t>20082445</t>
+  </si>
+  <si>
+    <t>MP BB WIPES N/FR BDD</t>
+  </si>
+  <si>
+    <t>10026930</t>
+  </si>
+  <si>
+    <t>JHNSN H&amp;B MLK+RC 200</t>
+  </si>
+  <si>
+    <t>20008706</t>
+  </si>
+  <si>
+    <t>MASTER CLG SPRMN 100</t>
+  </si>
+  <si>
+    <t>20130478</t>
+  </si>
+  <si>
+    <t>DOREMI COLG GLACR100</t>
+  </si>
+  <si>
+    <t>10031470</t>
+  </si>
+  <si>
+    <t>MY BABY PWD S.FLO225</t>
+  </si>
+  <si>
+    <t>10011772</t>
+  </si>
+  <si>
+    <t>CUSSONS B/CRM MILD50</t>
+  </si>
+  <si>
+    <t>10033930</t>
+  </si>
+  <si>
+    <t>CUSSON B/CRM SOFT50</t>
+  </si>
+  <si>
+    <t>20020120</t>
+  </si>
+  <si>
+    <t>CUSSON H&amp;BW ML&amp;G 375</t>
+  </si>
+  <si>
+    <t>20135778</t>
+  </si>
+  <si>
+    <t>CSSONS H&amp;B DP.MST375</t>
+  </si>
+  <si>
+    <t>20135637</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 300</t>
+  </si>
+  <si>
+    <t>20115501</t>
+  </si>
+  <si>
+    <t>KODOMO P/G MIXBRY45</t>
+  </si>
+  <si>
+    <t>20062263</t>
+  </si>
+  <si>
+    <t>PIGEON PRS NPL L 3'S</t>
   </si>
   <si>
     <t>RT</t>
@@ -667,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -754,7 +760,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -774,15 +780,15 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -791,10 +797,10 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -814,15 +820,15 @@
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -834,15 +840,15 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -854,7 +860,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -874,7 +880,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -891,18 +897,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -911,58 +917,58 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -971,18 +977,18 @@
         <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -991,10 +997,10 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1011,18 +1017,18 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1031,78 +1037,78 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1111,18 +1117,18 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1131,18 +1137,18 @@
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1151,18 +1157,18 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1171,190 +1177,210 @@
         <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>87</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
